--- a/downloads/monthly-budget.xlsx
+++ b/downloads/monthly-budget.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תקציב חודשי" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'תקציב חודשי'!$A$1:$E$1,'תקציב חודשי'!$A$4:$E$19</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -520,7 +522,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -855,5 +857,6 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/downloads/monthly-budget.xlsx
+++ b/downloads/monthly-budget.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תקציב חודשי" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'תקציב חודשי'!$A$1:$E$1,'תקציב חודשי'!$A$4:$E$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'תקציב חודשי'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" hidden="1" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>מלאו את העמודות "מתוכנן" ו"בפועל" (התאים הצהובים) — הסה"כ מתעדכן אוטומטית</t>
